--- a/data/daily/2026-09/2026-09-05.xlsx
+++ b/data/daily/2026-09/2026-09-05.xlsx
@@ -11,9 +11,7 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1270,132 +1268,132 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1525,642 +1523,132 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="457200" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2766,7 +2254,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2774,34 +2262,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2809,27 +2297,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
         </is>
       </c>
     </row>
@@ -2844,27 +2332,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11090567</t>
+          <t>https://gift.kakao.com/product/5551542</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703113258_219f277f4a66466ea414f5539beed475.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
         </is>
       </c>
     </row>
@@ -3011,7 +2499,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3019,34 +2507,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3054,27 +2542,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
@@ -3364,12 +2852,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -3421,17 +2909,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>종근당건강</t>
         </is>
       </c>
     </row>
@@ -3478,17 +2966,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
+          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
         </is>
       </c>
     </row>
@@ -3535,17 +3023,17 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <t>59,800원</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>15,900원</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3196,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3765,12 +3253,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>셀렉스</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>그레인온</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3822,12 +3310,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
           <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3879,12 +3367,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>24,900원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -4054,7 +3542,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,34 +3550,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,7 +3585,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4112,19 +3600,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +3620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4142,24 +3630,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,7 +3655,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4182,19 +3670,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,12 +3690,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,19 +3705,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,34 +3725,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624078&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/LCCefMiAcRv8JhM7m90p913624078_00_00LCCefMiAcRv8JhM7m90p.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +3760,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +3775,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,34 +3795,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,12 +3830,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 글루타치온 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +3845,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +3865,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +3880,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4000,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>홍삼/인삼</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4057,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4589,32 +4077,32 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>동국제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4114,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
+          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
+          <t>대웅제약 글루타치온 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>동국제약 이너케어＆유산균 30캡슐</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4171,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -4693,32 +4181,32 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4816,820 +4304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>이미지</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>가격</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>상품URL</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>이미지URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[9/5 하루특가] 지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>26,000원</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492945ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="38" customHeight="1">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[9/5 하루특가/스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>17,820원</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>31,300원</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014343ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>24,460원</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>13,320원</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>34,010원</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>플랫폼</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>1위</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>2위</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>3위</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>4위</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>5위</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>6위</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>7위</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>8위</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>9위</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>10위</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="100" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>썸네일</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>카테고리</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>알디콤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>닥터아돌</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>상품명</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>[9/5 하루특가] 지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[9/5 하루특가/스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>판매가</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>26,000원</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>17,820원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>31,300원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>24,460원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>13,320원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>34,010원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>바로가기</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A7"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5658,32 +4333,24 @@
           <t>다이소몰</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>올리브영</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>26.7</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5693,54 +4360,48 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -5748,9 +4409,6 @@
       <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5762,7 +4420,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -5770,65 +4428,56 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -5836,52 +4485,24 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily/2026-09/2026-09-05.xlsx
+++ b/data/daily/2026-09/2026-09-05.xlsx
@@ -11,7 +11,9 @@
     <sheet name="카카오선물하기_카드형" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="다이소몰" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet name="다이소몰_카드형" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="카테고리통계" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="올리브영" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="올리브영_카드형" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="카테고리통계" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1268,14 +1270,39 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1290,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1315,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1340,60 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="323850" cy="457200"/>
+    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1523,9 +1525,264 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1543,12 +1800,267 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="457200" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1573,7 +2085,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1598,7 +2110,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1623,7 +2135,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1648,7 +2160,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
+    <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2254,7 +2766,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2262,34 +2774,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2297,27 +2809,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
@@ -2332,27 +2844,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/5551542</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703113258_219f277f4a66466ea414f5539beed475.jpg</t>
         </is>
       </c>
     </row>
@@ -2499,7 +3011,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2507,34 +3019,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2542,27 +3054,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
         </is>
       </c>
     </row>
@@ -2852,12 +3364,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -2909,17 +3421,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>옵티젠</t>
         </is>
       </c>
     </row>
@@ -2966,17 +3478,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3535,17 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <t>52,900원</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,900원</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3708,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -3253,12 +3765,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3310,12 +3822,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3367,12 +3879,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -3542,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3550,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157053&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260327/PrU3TzDbYVJKWXoKyRxC919157053_00_01PrU3TzDbYVJKWXoKyRxC.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3585,7 +4097,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3600,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3620,7 +4132,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3630,24 +4142,24 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3655,7 +4167,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3670,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3690,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3705,19 +4217,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3725,34 +4237,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>오브맘 스트레스,쉼 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624078&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250519/LCCefMiAcRv8JhM7m90p913624078_00_00LCCefMiAcRv8JhM7m90p.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3760,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3775,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3795,34 +4307,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3830,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3845,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627142&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260612/IiBr1SI0rlUycwbkaeGq032627142_00_01IiBr1SI0rlUycwbkaeGq.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3865,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3880,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
         </is>
       </c>
     </row>
@@ -4000,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4569,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -4077,32 +4589,32 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>자연관</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>오브맘</t>
         </is>
       </c>
     </row>
@@ -4114,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
+          <t>휴럼 하루한포 6년근 고려홍삼 5포 5일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>오브맘 스트레스,쉼 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>자연관 리프레쉬 마그네슘＆L-테아닌 4병 4일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>오브맘 다이어트 홀릭 30포 15일분</t>
         </is>
       </c>
     </row>
@@ -4171,42 +4683,42 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -4304,7 +4816,820 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이미지</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>가격</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>상품URL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>이미지URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[9/5 하루특가] 지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492945ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[9/5 하루특가/스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17,820원</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355476ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="38" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014343ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="38" customHeight="1">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>24,460원</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733450ko.png?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13,320원</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584019ko.png?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>34,010원</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549618ko.jpg?l=ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>닥터아돌</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807373ko.png?l=ko</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1위</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2위</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>3위</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>4위</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>5위</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>6위</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>7위</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>8위</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>9위</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>10위</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>썸네일</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>브랜드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>락토핏</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>판도라</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>알디콤</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>닥터아돌</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>상품명</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>[9/5 하루특가] 지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[9/5 하루특가/스테디셀러 특가] 락토핏 골드 트리플 기획 (3개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[스테디셀러 특가][감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] [반값특가] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 (+시나모롤 틴케이스 키링)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>17,820원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>31,300원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>14,900원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>24,460원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>13,320원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>34,010원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>바로가기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4333,24 +5658,32 @@
           <t>다이소몰</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>26.7</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -4360,48 +5693,54 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>23.3</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -4409,6 +5748,9 @@
       <c r="E5" t="n">
         <v>2</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4420,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -4428,56 +5770,65 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -4485,24 +5836,52 @@
       <c r="E9" t="n">
         <v>1</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
